--- a/Timesheet-Project/Timesheet 3/Buhle/Buhle_Mukhuba_March_FinalWeek.xlsx
+++ b/Timesheet-Project/Timesheet 3/Buhle/Buhle_Mukhuba_March_FinalWeek.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sc_LwazisileMhlambi_2026\Timesheet-Project\Timesheet 3\Buhle\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://northerndata-my.sharepoint.com/personal/buhle_mukhuba_sambeconsulting_com/Documents/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="75" documentId="8_{7E45E865-ED97-4E5F-8A35-A2A68DE5DF4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B08C5DF0-3CFA-445B-B5E8-7A628D8C814D}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8880" xr2:uid="{1C8F8026-B005-4B08-94D3-371A77F74D8F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1C8F8026-B005-4B08-94D3-371A77F74D8F}"/>
   </bookViews>
   <sheets>
     <sheet name="Mar" sheetId="6" r:id="rId1"/>
     <sheet name="Key" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1763,6 +1764,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2E876225-7964-4082-91F1-C6221C464408}" name="WorkType" displayName="WorkType" ref="H2:H77" totalsRowShown="0" headerRowDxfId="24" dataDxfId="23">
   <autoFilter ref="H2:H77" xr:uid="{2E876225-7964-4082-91F1-C6221C464408}"/>
@@ -8213,21 +8218,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100AD10A028B4ACBB47B37340D8D4079B36" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="436e80374471046821afb96e56969fce">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="606bf0c3-7c02-4ad1-9a2b-bad21eeec9a2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="819cb4b524acab89028d2f2d821df341" ns2:_="">
     <xsd:import namespace="606bf0c3-7c02-4ad1-9a2b-bad21eeec9a2"/>
@@ -8365,39 +8355,31 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{615D0308-A962-4273-9D27-8D7E6C533D14}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61C263E3-2AA1-43E0-8AC9-C7C66277B332}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BE13FA5-2B48-4235-B442-8317F2373CFA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BE13FA5-2B48-4235-B442-8317F2373CFA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61C263E3-2AA1-43E0-8AC9-C7C66277B332}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="606bf0c3-7c02-4ad1-9a2b-bad21eeec9a2"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{615D0308-A962-4273-9D27-8D7E6C533D14}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
